--- a/CLM_Enterprise_Features.xlsx
+++ b/CLM_Enterprise_Features.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\stbuckme\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\stbuckme\vibe\claim-arch\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{466AFCDE-44A0-4045-96E6-DDE537EF07AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9A56396-1C89-4050-8BDA-636EBD7CA1DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7470" yWindow="1500" windowWidth="29040" windowHeight="18795" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2160" yWindow="2025" windowWidth="32775" windowHeight="18795" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CLM Features" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="379">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="380">
   <si>
     <t>Priority</t>
   </si>
@@ -1157,6 +1157,9 @@
   </si>
   <si>
     <t>Office Add-in manifest Word plus Outlook hosted on Azure Static Web Apps. Word: insert approved clauses, send for approval, check status inline. Outlook: create contract from email thread, link email to existing contract. Microsoft Graph API for email and calendar access. Include redlining that leverages AI and ML capabilities.</t>
+  </si>
+  <si>
+    <t>FeatureID</t>
   </si>
 </sst>
 </file>
@@ -1178,7 +1181,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1208,6 +1211,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFCCFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F3864"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -1334,7 +1349,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1390,45 +1405,20 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="12">
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <name val="Calibri"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF1F3864"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FFCCCCCC"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFCCCCCC"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
+  <dxfs count="13">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1437,6 +1427,22 @@
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFCCCCCC"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFCCCCCC"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFCCCCCC"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFCCCCCC"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
     </dxf>
     <dxf>
       <fill>
@@ -1618,13 +1624,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="thin">
-          <color rgb="FFCCCCCC"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
         <left style="thin">
           <color rgb="FFCCCCCC"/>
         </left>
@@ -1637,6 +1636,56 @@
         <bottom style="thin">
           <color rgb="FFCCCCCC"/>
         </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFCCFFCC"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color rgb="FFCCCCCC"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Calibri"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF1F3864"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FFCCCCCC"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFCCCCCC"/>
+        </right>
+        <top/>
+        <bottom/>
       </border>
     </dxf>
   </dxfs>
@@ -1653,16 +1702,17 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{72502ED8-ECB4-4930-871C-52C6FE0EEFD7}" name="Table1" displayName="Table1" ref="A1:G72" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1" headerRowBorderDxfId="10" tableBorderDxfId="11" totalsRowBorderDxfId="9">
-  <autoFilter ref="A1:G72" xr:uid="{72502ED8-ECB4-4930-871C-52C6FE0EEFD7}"/>
-  <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{957ED9A9-DE1C-4DC4-BE5A-F35A27BA9B51}" name="Priority" dataDxfId="8"/>
-    <tableColumn id="2" xr3:uid="{6A797C80-8BB1-4F14-804C-4992F99018AB}" name="Feature Category" dataDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{D510290E-6DC8-4B29-B8F2-C8809CCF599D}" name="Feature Name" dataDxfId="6"/>
-    <tableColumn id="4" xr3:uid="{585F3167-E298-487F-BFE2-3661B9FEDD0C}" name="Feature Description" dataDxfId="5"/>
-    <tableColumn id="5" xr3:uid="{5D55B52D-A2BE-43CF-A129-ADC77D815A38}" name="Technical Requirement (Azure / Kubernetes)" dataDxfId="4"/>
-    <tableColumn id="6" xr3:uid="{E7B55B50-4821-488C-860A-C54AC6BBE86B}" name="Azure Service(s)" dataDxfId="3"/>
-    <tableColumn id="7" xr3:uid="{B446272C-C714-45B6-9906-C67C5F378EAA}" name="Notes" dataDxfId="2"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{72502ED8-ECB4-4930-871C-52C6FE0EEFD7}" name="Table1" displayName="Table1" ref="A1:H72" totalsRowShown="0" headerRowDxfId="12" dataDxfId="10" headerRowBorderDxfId="11" tableBorderDxfId="9" totalsRowBorderDxfId="8">
+  <autoFilter ref="A1:H72" xr:uid="{72502ED8-ECB4-4930-871C-52C6FE0EEFD7}"/>
+  <tableColumns count="8">
+    <tableColumn id="1" xr3:uid="{957ED9A9-DE1C-4DC4-BE5A-F35A27BA9B51}" name="Priority" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{6A797C80-8BB1-4F14-804C-4992F99018AB}" name="Feature Category" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{D510290E-6DC8-4B29-B8F2-C8809CCF599D}" name="Feature Name" dataDxfId="5"/>
+    <tableColumn id="4" xr3:uid="{585F3167-E298-487F-BFE2-3661B9FEDD0C}" name="Feature Description" dataDxfId="4"/>
+    <tableColumn id="5" xr3:uid="{5D55B52D-A2BE-43CF-A129-ADC77D815A38}" name="Technical Requirement (Azure / Kubernetes)" dataDxfId="3"/>
+    <tableColumn id="6" xr3:uid="{E7B55B50-4821-488C-860A-C54AC6BBE86B}" name="Azure Service(s)" dataDxfId="2"/>
+    <tableColumn id="7" xr3:uid="{B446272C-C714-45B6-9906-C67C5F378EAA}" name="Notes" dataDxfId="1"/>
+    <tableColumn id="8" xr3:uid="{5DC30F3C-C0BE-44C7-A734-9EB056510A1F}" name="FeatureID" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1953,8 +2003,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G72"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:H72"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
@@ -1965,7 +2015,7 @@
     <col min="7" max="7" width="32" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
@@ -1987,8 +2037,11 @@
       <c r="G1" s="15" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H1" s="21" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>7</v>
       </c>
@@ -2010,8 +2063,11 @@
       <c r="G2" s="9" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H2" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>7</v>
       </c>
@@ -2033,8 +2089,11 @@
       <c r="G3" s="9" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H3" s="19">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>7</v>
       </c>
@@ -2056,8 +2115,11 @@
       <c r="G4" s="9" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H4" s="20">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>7</v>
       </c>
@@ -2079,8 +2141,11 @@
       <c r="G5" s="9" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H5" s="19">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>7</v>
       </c>
@@ -2102,8 +2167,11 @@
       <c r="G6" s="9" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H6" s="20">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>7</v>
       </c>
@@ -2125,8 +2193,11 @@
       <c r="G7" s="9" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H7" s="19">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>7</v>
       </c>
@@ -2148,8 +2219,11 @@
       <c r="G8" s="9" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H8" s="20">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>7</v>
       </c>
@@ -2171,8 +2245,11 @@
       <c r="G9" s="9" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H9" s="19">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>7</v>
       </c>
@@ -2194,8 +2271,11 @@
       <c r="G10" s="9" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H10" s="20">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>7</v>
       </c>
@@ -2217,8 +2297,11 @@
       <c r="G11" s="9" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H11" s="19">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>7</v>
       </c>
@@ -2240,8 +2323,11 @@
       <c r="G12" s="9" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H12" s="20">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>7</v>
       </c>
@@ -2263,8 +2349,11 @@
       <c r="G13" s="9" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H13" s="19">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>7</v>
       </c>
@@ -2286,8 +2375,11 @@
       <c r="G14" s="9" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H14" s="20">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
         <v>7</v>
       </c>
@@ -2309,8 +2401,11 @@
       <c r="G15" s="9" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H15" s="19">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
         <v>7</v>
       </c>
@@ -2332,8 +2427,11 @@
       <c r="G16" s="9" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H16" s="20">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
         <v>7</v>
       </c>
@@ -2355,8 +2453,11 @@
       <c r="G17" s="9" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H17" s="19">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
         <v>7</v>
       </c>
@@ -2378,8 +2479,11 @@
       <c r="G18" s="9" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H18" s="20">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
         <v>7</v>
       </c>
@@ -2401,8 +2505,11 @@
       <c r="G19" s="9" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H19" s="19">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
         <v>7</v>
       </c>
@@ -2424,8 +2531,11 @@
       <c r="G20" s="9" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H20" s="20">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
         <v>108</v>
       </c>
@@ -2447,8 +2557,11 @@
       <c r="G21" s="10" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H21" s="19">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
         <v>108</v>
       </c>
@@ -2470,8 +2583,11 @@
       <c r="G22" s="10" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="23" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H22" s="20">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
         <v>108</v>
       </c>
@@ -2493,8 +2609,11 @@
       <c r="G23" s="10" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="24" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H23" s="19">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
         <v>108</v>
       </c>
@@ -2516,8 +2635,11 @@
       <c r="G24" s="10" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="25" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H24" s="20">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
         <v>108</v>
       </c>
@@ -2539,8 +2661,11 @@
       <c r="G25" s="10" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="26" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H25" s="19">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
         <v>108</v>
       </c>
@@ -2562,8 +2687,11 @@
       <c r="G26" s="10" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="27" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H26" s="20">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
         <v>108</v>
       </c>
@@ -2585,8 +2713,11 @@
       <c r="G27" s="10" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="28" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H27" s="19">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
         <v>108</v>
       </c>
@@ -2608,8 +2739,11 @@
       <c r="G28" s="10" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="29" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H28" s="20">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
         <v>108</v>
       </c>
@@ -2631,8 +2765,11 @@
       <c r="G29" s="10" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="30" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H29" s="19">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
         <v>108</v>
       </c>
@@ -2654,8 +2791,11 @@
       <c r="G30" s="10" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="31" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H30" s="20">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
         <v>108</v>
       </c>
@@ -2677,8 +2817,11 @@
       <c r="G31" s="10" t="s">
         <v>165</v>
       </c>
-    </row>
-    <row r="32" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H31" s="19">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
         <v>108</v>
       </c>
@@ -2700,8 +2843,11 @@
       <c r="G32" s="10" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="33" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H32" s="20">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
         <v>108</v>
       </c>
@@ -2723,8 +2869,11 @@
       <c r="G33" s="10" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="34" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H33" s="19">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
         <v>108</v>
       </c>
@@ -2746,8 +2895,11 @@
       <c r="G34" s="10" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="35" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H34" s="20">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="6" t="s">
         <v>108</v>
       </c>
@@ -2769,8 +2921,11 @@
       <c r="G35" s="10" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="36" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H35" s="19">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
         <v>108</v>
       </c>
@@ -2792,8 +2947,11 @@
       <c r="G36" s="10" t="s">
         <v>192</v>
       </c>
-    </row>
-    <row r="37" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H36" s="20">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="6" t="s">
         <v>108</v>
       </c>
@@ -2815,8 +2973,11 @@
       <c r="G37" s="10" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="38" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H37" s="19">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
         <v>108</v>
       </c>
@@ -2838,8 +2999,11 @@
       <c r="G38" s="10" t="s">
         <v>201</v>
       </c>
-    </row>
-    <row r="39" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H38" s="20">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="6" t="s">
         <v>108</v>
       </c>
@@ -2861,8 +3025,11 @@
       <c r="G39" s="10" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="40" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H39" s="19">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="6" t="s">
         <v>108</v>
       </c>
@@ -2884,8 +3051,11 @@
       <c r="G40" s="10" t="s">
         <v>211</v>
       </c>
-    </row>
-    <row r="41" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H40" s="20">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="6" t="s">
         <v>108</v>
       </c>
@@ -2907,8 +3077,11 @@
       <c r="G41" s="10" t="s">
         <v>216</v>
       </c>
-    </row>
-    <row r="42" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H41" s="19">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="7" t="s">
         <v>217</v>
       </c>
@@ -2930,8 +3103,11 @@
       <c r="G42" s="11" t="s">
         <v>222</v>
       </c>
-    </row>
-    <row r="43" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H42" s="20">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
         <v>217</v>
       </c>
@@ -2953,8 +3129,11 @@
       <c r="G43" s="11" t="s">
         <v>227</v>
       </c>
-    </row>
-    <row r="44" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H43" s="19">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="7" t="s">
         <v>217</v>
       </c>
@@ -2976,8 +3155,11 @@
       <c r="G44" s="11" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="45" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H44" s="20">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
         <v>217</v>
       </c>
@@ -2999,8 +3181,11 @@
       <c r="G45" s="11" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="46" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H45" s="19">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="7" t="s">
         <v>217</v>
       </c>
@@ -3022,8 +3207,11 @@
       <c r="G46" s="11" t="s">
         <v>242</v>
       </c>
-    </row>
-    <row r="47" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H46" s="20">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
         <v>217</v>
       </c>
@@ -3045,8 +3233,11 @@
       <c r="G47" s="11" t="s">
         <v>247</v>
       </c>
-    </row>
-    <row r="48" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H47" s="19">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="7" t="s">
         <v>217</v>
       </c>
@@ -3068,8 +3259,11 @@
       <c r="G48" s="11" t="s">
         <v>252</v>
       </c>
-    </row>
-    <row r="49" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H48" s="20">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
         <v>217</v>
       </c>
@@ -3091,8 +3285,11 @@
       <c r="G49" s="11" t="s">
         <v>257</v>
       </c>
-    </row>
-    <row r="50" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H49" s="19">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="7" t="s">
         <v>217</v>
       </c>
@@ -3114,8 +3311,11 @@
       <c r="G50" s="11" t="s">
         <v>263</v>
       </c>
-    </row>
-    <row r="51" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H50" s="20">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
         <v>217</v>
       </c>
@@ -3137,8 +3337,11 @@
       <c r="G51" s="11" t="s">
         <v>268</v>
       </c>
-    </row>
-    <row r="52" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H51" s="19">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="7" t="s">
         <v>217</v>
       </c>
@@ -3160,8 +3363,11 @@
       <c r="G52" s="11" t="s">
         <v>273</v>
       </c>
-    </row>
-    <row r="53" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H52" s="20">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
         <v>217</v>
       </c>
@@ -3183,8 +3389,11 @@
       <c r="G53" s="11" t="s">
         <v>278</v>
       </c>
-    </row>
-    <row r="54" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H53" s="19">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="7" t="s">
         <v>217</v>
       </c>
@@ -3206,8 +3415,11 @@
       <c r="G54" s="11" t="s">
         <v>283</v>
       </c>
-    </row>
-    <row r="55" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H54" s="20">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
         <v>217</v>
       </c>
@@ -3229,8 +3441,11 @@
       <c r="G55" s="11" t="s">
         <v>289</v>
       </c>
-    </row>
-    <row r="56" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H55" s="19">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="7" t="s">
         <v>217</v>
       </c>
@@ -3252,8 +3467,11 @@
       <c r="G56" s="11" t="s">
         <v>294</v>
       </c>
-    </row>
-    <row r="57" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H56" s="20">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
         <v>217</v>
       </c>
@@ -3275,8 +3493,11 @@
       <c r="G57" s="11" t="s">
         <v>299</v>
       </c>
-    </row>
-    <row r="58" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H57" s="19">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="7" t="s">
         <v>217</v>
       </c>
@@ -3298,8 +3519,11 @@
       <c r="G58" s="11" t="s">
         <v>304</v>
       </c>
-    </row>
-    <row r="59" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H58" s="20">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
         <v>217</v>
       </c>
@@ -3321,8 +3545,11 @@
       <c r="G59" s="11" t="s">
         <v>309</v>
       </c>
-    </row>
-    <row r="60" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H59" s="19">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="8" t="s">
         <v>310</v>
       </c>
@@ -3344,8 +3571,11 @@
       <c r="G60" s="12" t="s">
         <v>315</v>
       </c>
-    </row>
-    <row r="61" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H60" s="20">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
         <v>310</v>
       </c>
@@ -3367,8 +3597,11 @@
       <c r="G61" s="12" t="s">
         <v>320</v>
       </c>
-    </row>
-    <row r="62" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H61" s="19">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="8" t="s">
         <v>310</v>
       </c>
@@ -3390,8 +3623,11 @@
       <c r="G62" s="12" t="s">
         <v>325</v>
       </c>
-    </row>
-    <row r="63" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H62" s="20">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
         <v>310</v>
       </c>
@@ -3413,8 +3649,11 @@
       <c r="G63" s="12" t="s">
         <v>330</v>
       </c>
-    </row>
-    <row r="64" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H63" s="19">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="8" t="s">
         <v>310</v>
       </c>
@@ -3436,8 +3675,11 @@
       <c r="G64" s="12" t="s">
         <v>335</v>
       </c>
-    </row>
-    <row r="65" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H64" s="20">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
         <v>310</v>
       </c>
@@ -3459,8 +3701,11 @@
       <c r="G65" s="12" t="s">
         <v>339</v>
       </c>
-    </row>
-    <row r="66" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H65" s="19">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="8" t="s">
         <v>310</v>
       </c>
@@ -3482,8 +3727,11 @@
       <c r="G66" s="12" t="s">
         <v>344</v>
       </c>
-    </row>
-    <row r="67" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H66" s="20">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
         <v>310</v>
       </c>
@@ -3505,8 +3753,11 @@
       <c r="G67" s="12" t="s">
         <v>349</v>
       </c>
-    </row>
-    <row r="68" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H67" s="19">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="8" t="s">
         <v>310</v>
       </c>
@@ -3528,8 +3779,11 @@
       <c r="G68" s="12" t="s">
         <v>354</v>
       </c>
-    </row>
-    <row r="69" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H68" s="20">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
         <v>310</v>
       </c>
@@ -3551,8 +3805,11 @@
       <c r="G69" s="12" t="s">
         <v>359</v>
       </c>
-    </row>
-    <row r="70" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H69" s="19">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="8" t="s">
         <v>310</v>
       </c>
@@ -3574,8 +3831,11 @@
       <c r="G70" s="12" t="s">
         <v>364</v>
       </c>
-    </row>
-    <row r="71" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H70" s="20">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
         <v>310</v>
       </c>
@@ -3597,8 +3857,11 @@
       <c r="G71" s="12" t="s">
         <v>369</v>
       </c>
-    </row>
-    <row r="72" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H71" s="19">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="16" t="s">
         <v>310</v>
       </c>
@@ -3619,6 +3882,9 @@
       </c>
       <c r="G72" s="18" t="s">
         <v>374</v>
+      </c>
+      <c r="H72" s="20">
+        <v>71</v>
       </c>
     </row>
   </sheetData>
